--- a/data/performance/daily/signal_list_2026-06-08.xlsx
+++ b/data/performance/daily/signal_list_2026-06-08.xlsx
@@ -41,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -74,6 +84,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 0.0%  (0W / 0L of 0 evaluated, 7 pending)</t>
+          <t>Win Rate: 57.1%  (4W / 3L of 7 evaluated)</t>
         </is>
       </c>
     </row>
@@ -531,11 +543,34 @@
           <t>BREAKOUT</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="C5" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2460</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -550,11 +585,34 @@
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="C6" t="n">
+        <v>5925</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5950</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -569,11 +627,34 @@
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="C7" t="n">
+        <v>7850</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8325</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -588,11 +669,34 @@
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="C8" t="n">
+        <v>496</v>
+      </c>
+      <c r="D8" t="n">
+        <v>560</v>
+      </c>
+      <c r="E8" t="n">
+        <v>570</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -607,11 +711,34 @@
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="C9" t="n">
+        <v>165</v>
+      </c>
+      <c r="D9" t="n">
+        <v>143</v>
+      </c>
+      <c r="E9" t="n">
+        <v>210</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-13.33</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -626,11 +753,34 @@
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="C10" t="n">
+        <v>113</v>
+      </c>
+      <c r="D10" t="n">
+        <v>106</v>
+      </c>
+      <c r="E10" t="n">
+        <v>113</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-6.19</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -645,11 +795,34 @@
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="C11" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1095</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1095</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -689,7 +862,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 0.0%  (0W / 0L of 0 evaluated, 13 pending)</t>
+          <t>Win Rate: 41.7%  (5W / 7L of 12 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -756,11 +929,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="C5" t="n">
+        <v>246</v>
+      </c>
+      <c r="D5" t="n">
+        <v>252</v>
+      </c>
+      <c r="E5" t="n">
+        <v>286</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -775,11 +971,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="C6" t="n">
+        <v>6450</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6350</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6725</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -794,11 +1013,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="C7" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2460</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -813,11 +1055,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="C8" t="n">
+        <v>118</v>
+      </c>
+      <c r="D8" t="n">
+        <v>105</v>
+      </c>
+      <c r="E8" t="n">
+        <v>122</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-11.02</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -832,11 +1097,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="C9" t="n">
+        <v>655</v>
+      </c>
+      <c r="D9" t="n">
+        <v>655</v>
+      </c>
+      <c r="E9" t="n">
+        <v>655</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -851,11 +1139,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="C10" t="n">
+        <v>266</v>
+      </c>
+      <c r="D10" t="n">
+        <v>270</v>
+      </c>
+      <c r="E10" t="n">
+        <v>278</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -870,11 +1181,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="C11" t="n">
+        <v>580</v>
+      </c>
+      <c r="D11" t="n">
+        <v>570</v>
+      </c>
+      <c r="E11" t="n">
+        <v>590</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -889,11 +1223,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="C12" t="n">
+        <v>270</v>
+      </c>
+      <c r="D12" t="n">
+        <v>268</v>
+      </c>
+      <c r="E12" t="n">
+        <v>272</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -908,11 +1265,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="C13" t="n">
+        <v>169</v>
+      </c>
+      <c r="D13" t="n">
+        <v>191</v>
+      </c>
+      <c r="E13" t="n">
+        <v>226</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -927,11 +1307,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="C14" t="n">
+        <v>7850</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8325</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -946,8 +1349,21 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="C15" t="n">
+        <v/>
+      </c>
+      <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
+        <v/>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v/>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>pending</t>
@@ -965,11 +1381,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="C16" t="n">
+        <v>165</v>
+      </c>
+      <c r="D16" t="n">
+        <v>143</v>
+      </c>
+      <c r="E16" t="n">
+        <v>210</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-13.33</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -984,11 +1423,34 @@
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="C17" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1095</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1095</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>

--- a/data/performance/daily/signal_list_2026-06-08.xlsx
+++ b/data/performance/daily/signal_list_2026-06-08.xlsx
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 57.1%  (4W / 3L of 7 evaluated)</t>
+          <t>Win Rate: 71.4%  (5W / 2L of 7 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2490</v>
+        <v>2020</v>
       </c>
       <c r="D5" t="n">
         <v>2460</v>
@@ -553,14 +553,14 @@
         <v>2520</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.2</v>
+        <v>24.75</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-1.2</v>
+        <v>21.78</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -600,7 +600,7 @@
       <c r="G6" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7850</v>
+        <v>8050</v>
       </c>
       <c r="D7" t="n">
         <v>8325</v>
@@ -637,12 +637,12 @@
         <v>8400</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.01</v>
+        <v>4.35</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+        <v>3.42</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
         <v>560</v>
@@ -679,12 +679,12 @@
         <v>570</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14.92</v>
+        <v>14.46</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+        <v>12.45</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D9" t="n">
         <v>143</v>
@@ -721,12 +721,12 @@
         <v>210</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-13.33</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+        <v>-14.88</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D10" t="n">
         <v>106</v>
@@ -763,12 +763,12 @@
         <v>113</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.19</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
+        <v>-0.93</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1040</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="n">
         <v>1095</v>
@@ -805,12 +805,12 @@
         <v>1095</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.29</v>
+        <v>9.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+        <v>9.5</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -862,7 +862,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 41.7%  (5W / 7L of 12 evaluated, 1 pending)</t>
+          <t>Win Rate: 33.3%  (4W / 8L of 12 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="D5" t="n">
         <v>252</v>
@@ -939,14 +939,14 @@
         <v>286</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16.26</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.44</v>
+        <v>-12.5</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6450</v>
+        <v>7450</v>
       </c>
       <c r="D6" t="n">
         <v>6350</v>
@@ -981,12 +981,12 @@
         <v>6725</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.26</v>
+        <v>-9.73</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+        <v>-14.77</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2490</v>
+        <v>2020</v>
       </c>
       <c r="D7" t="n">
         <v>2460</v>
@@ -1023,14 +1023,14 @@
         <v>2520</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.2</v>
+        <v>24.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.2</v>
+        <v>21.78</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D8" t="n">
         <v>105</v>
@@ -1065,12 +1065,12 @@
         <v>122</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.39</v>
+        <v>0.83</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-11.02</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+        <v>-13.22</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D9" t="n">
         <v>655</v>
@@ -1107,12 +1107,12 @@
         <v>655</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+        <v>-0.76</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D10" t="n">
         <v>270</v>
@@ -1149,12 +1149,12 @@
         <v>278</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.51</v>
+        <v>3.73</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+        <v>0.75</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1196,7 +1196,7 @@
       <c r="G11" s="4" t="n">
         <v>-1.72</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1238,7 +1238,7 @@
       <c r="G12" s="4" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="D13" t="n">
         <v>191</v>
@@ -1275,14 +1275,14 @@
         <v>226</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>33.73</v>
+        <v>15.31</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>13.02</v>
+        <v>-2.55</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7850</v>
+        <v>8050</v>
       </c>
       <c r="D14" t="n">
         <v>8325</v>
@@ -1317,12 +1317,12 @@
         <v>8400</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7.01</v>
+        <v>4.35</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+        <v>3.42</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D16" t="n">
         <v>143</v>
@@ -1391,12 +1391,12 @@
         <v>210</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-13.33</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+        <v>-14.88</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1040</v>
+        <v>1000</v>
       </c>
       <c r="D17" t="n">
         <v>1095</v>
@@ -1433,12 +1433,12 @@
         <v>1095</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.29</v>
+        <v>9.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+        <v>9.5</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-08.xlsx
+++ b/data/performance/daily/signal_list_2026-06-08.xlsx
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-06-08</t>
+          <t>Swing — Review sesi market 2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 71.4%  (5W / 2L of 7 evaluated)</t>
+          <t>Win Rate: 0.0%  (0W / 6L of 6 evaluated)</t>
         </is>
       </c>
     </row>
@@ -535,37 +535,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>APLI.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>PRE_MARKUP</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2020</v>
+        <v>293.97</v>
       </c>
       <c r="D5" t="n">
-        <v>2460</v>
+        <v>288</v>
       </c>
       <c r="E5" t="n">
-        <v>2520</v>
+        <v>288</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>24.75</v>
+        <v>-2.03</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>21.78</v>
+        <v>-2.03</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLBI.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -586,28 +586,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5925</v>
+        <v>1090</v>
       </c>
       <c r="D6" t="n">
-        <v>5950</v>
+        <v>900</v>
       </c>
       <c r="E6" t="n">
-        <v>6000</v>
+        <v>916.8200000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.27</v>
+        <v>-15.89</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.42</v>
+        <v>-17.43</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -628,28 +628,28 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>8200</v>
+      </c>
+      <c r="D7" t="n">
         <v>8050</v>
       </c>
-      <c r="D7" t="n">
-        <v>8325</v>
-      </c>
       <c r="E7" t="n">
-        <v>8400</v>
+        <v>8200</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.42</v>
+        <v>-1.83</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" t="n">
         <v>498</v>
       </c>
-      <c r="D8" t="n">
-        <v>560</v>
-      </c>
       <c r="E8" t="n">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14.46</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.45</v>
+        <v>-0.4</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="D9" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-14.88</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,73 +754,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D10" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.61</v>
+        <v>12.87</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>VISI.JK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PRE_MARKUP</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1095</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1095</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -837,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -855,14 +813,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-06-08</t>
+          <t>Scalping — Review sesi market 2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 33.3%  (4W / 8L of 12 evaluated, 1 pending)</t>
+          <t>Win Rate: 20.0%  (3W / 12L of 15 evaluated)</t>
         </is>
       </c>
     </row>
@@ -930,28 +888,28 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>293.97</v>
+      </c>
+      <c r="D5" t="n">
         <v>288</v>
       </c>
-      <c r="D5" t="n">
-        <v>252</v>
-      </c>
       <c r="E5" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-2.03</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
+        <v>-2.03</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -963,7 +921,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>BATA.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -972,28 +930,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7450</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>6350</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
-        <v>6725</v>
+        <v>65</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-9.73</v>
+        <v>-2.99</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.77</v>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+        <v>-4.48</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1005,7 +963,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1014,28 +972,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2020</v>
+        <v>6225</v>
       </c>
       <c r="D7" t="n">
-        <v>2460</v>
+        <v>7450</v>
       </c>
       <c r="E7" t="n">
-        <v>2520</v>
+        <v>7450</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>24.75</v>
+        <v>19.68</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+        <v>19.68</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1047,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,28 +1014,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>121</v>
+        <v>1620</v>
       </c>
       <c r="D8" t="n">
-        <v>105</v>
+        <v>2020</v>
       </c>
       <c r="E8" t="n">
-        <v>122</v>
+        <v>2020</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.83</v>
+        <v>24.69</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-13.22</v>
+        <v>24.69</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1089,7 +1047,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFCO.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1098,28 +1056,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>660</v>
+        <v>995</v>
       </c>
       <c r="D9" t="n">
-        <v>655</v>
+        <v>865</v>
       </c>
       <c r="E9" t="n">
-        <v>655</v>
+        <v>985</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.76</v>
+        <v>-1.01</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+        <v>-13.07</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1131,7 +1089,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DWGL.JK</t>
+          <t>SMMA.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1140,28 +1098,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>268</v>
+        <v>20000</v>
       </c>
       <c r="D10" t="n">
-        <v>270</v>
+        <v>20975</v>
       </c>
       <c r="E10" t="n">
-        <v>278</v>
+        <v>21000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.73</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
+        <v>4.88</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1173,7 +1131,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1182,28 +1140,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>580</v>
+        <v>230</v>
       </c>
       <c r="D11" t="n">
-        <v>570</v>
+        <v>196</v>
       </c>
       <c r="E11" t="n">
-        <v>590</v>
+        <v>234</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+        <v>-14.78</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1215,7 +1173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SATU.JK</t>
+          <t>MGLV.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1224,28 +1182,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>270</v>
+        <v>8200</v>
       </c>
       <c r="D12" t="n">
-        <v>268</v>
+        <v>8050</v>
       </c>
       <c r="E12" t="n">
-        <v>272</v>
+        <v>8200</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+        <v>-1.83</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1257,7 +1215,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>WGSH.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1266,28 +1224,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>196</v>
+        <v>141</v>
       </c>
       <c r="D13" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="E13" t="n">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>15.31</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+        <v>-9.93</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1299,7 +1257,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MGLV.JK</t>
+          <t>CBPE.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1308,28 +1266,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8050</v>
+        <v>324</v>
       </c>
       <c r="D14" t="n">
-        <v>8325</v>
+        <v>280</v>
       </c>
       <c r="E14" t="n">
-        <v>8400</v>
+        <v>314</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.35</v>
+        <v>-3.09</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.42</v>
+        <v>-13.58</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1341,7 +1299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>NAYZ.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1350,30 +1308,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v/>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v/>
+        <v>67</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v/>
+        <v>1.52</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v/>
+        <v>-9.09</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GRIA.JK</t>
+          <t>MUTU.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,28 +1350,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="D16" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-14.88</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1415,40 +1383,124 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>RGAS.JK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>101</v>
+      </c>
+      <c r="E17" t="n">
+        <v>114</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>VISI.JK</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>SCALPING_HIGH</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D18" t="n">
         <v>1000</v>
       </c>
-      <c r="D17" t="n">
-        <v>1095</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1095</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="E18" t="n">
+        <v>1065</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DAAZ.JK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1845</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-13.04</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-08.xlsx
+++ b/data/performance/daily/signal_list_2026-06-08.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-08.xlsx
+++ b/data/performance/daily/signal_list_2026-06-08.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-08.xlsx
+++ b/data/performance/daily/signal_list_2026-06-08.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -731,12 +757,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -795,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -805,9 +841,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,7 +874,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -862,15 +899,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -907,12 +949,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -949,12 +996,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -991,12 +1043,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1033,12 +1090,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1075,12 +1137,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,12 +1184,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1154,17 +1226,22 @@
       <c r="G11" s="4" t="n">
         <v>-14.78</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1201,12 +1278,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1243,12 +1325,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1285,12 +1372,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1322,17 +1414,22 @@
       <c r="G15" s="4" t="n">
         <v>-9.09</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1369,12 +1466,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1406,17 +1508,22 @@
       <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G18" s="4" t="n">
         <v>-2.91</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1490,17 +1602,22 @@
       <c r="G19" s="4" t="n">
         <v>-13.04</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-08.xlsx
+++ b/data/performance/daily/signal_list_2026-06-08.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -558,28 +564,31 @@
       <c r="E5" t="n">
         <v>288</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>-2.03</v>
+      <c r="F5" t="n">
+        <v>288</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>-2.03</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H5" s="4" t="n">
+        <v>-2.03</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>1090</v>
       </c>
       <c r="D6" t="n">
+        <v>916.8200000000001</v>
+      </c>
+      <c r="E6" t="n">
         <v>900</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>916.8200000000001</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>-15.89</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-17.43</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>8200</v>
       </c>
       <c r="D7" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E7" t="n">
         <v>8050</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>8200</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-1.83</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>500</v>
       </c>
       <c r="D8" t="n">
+        <v>496</v>
+      </c>
+      <c r="E8" t="n">
         <v>498</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>500</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>117</v>
       </c>
       <c r="D9" t="n">
+        <v>116</v>
+      </c>
+      <c r="E9" t="n">
         <v>107</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>117</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-8.550000000000001</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>101</v>
       </c>
       <c r="D10" t="n">
+        <v>93</v>
+      </c>
+      <c r="E10" t="n">
         <v>101</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>12.87</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -831,7 +855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -839,12 +863,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -874,45 +899,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -938,28 +968,31 @@
       <c r="E5" t="n">
         <v>288</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>-2.03</v>
+      <c r="F5" t="n">
+        <v>288</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>-2.03</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H5" s="4" t="n">
+        <v>-2.03</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -980,33 +1013,36 @@
         <v>67</v>
       </c>
       <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
         <v>64</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>65</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>-2.99</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-4.48</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1027,33 +1063,36 @@
         <v>6225</v>
       </c>
       <c r="D7" t="n">
-        <v>7450</v>
+        <v>6300</v>
       </c>
       <c r="E7" t="n">
         <v>7450</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>19.68</v>
+      <c r="F7" t="n">
+        <v>7450</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>19.68</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="4" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1074,33 +1113,36 @@
         <v>1620</v>
       </c>
       <c r="D8" t="n">
-        <v>2020</v>
+        <v>1625</v>
       </c>
       <c r="E8" t="n">
         <v>2020</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>24.69</v>
+      <c r="F8" t="n">
+        <v>2020</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>24.69</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="4" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1121,33 +1163,36 @@
         <v>995</v>
       </c>
       <c r="D9" t="n">
+        <v>985</v>
+      </c>
+      <c r="E9" t="n">
         <v>865</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>985</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>-1.01</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-13.07</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1168,33 +1213,36 @@
         <v>20000</v>
       </c>
       <c r="D10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E10" t="n">
         <v>20975</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>21000</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>4.88</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>230</v>
       </c>
       <c r="D11" t="n">
+        <v>228</v>
+      </c>
+      <c r="E11" t="n">
         <v>196</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>234</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>1.74</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-14.78</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>8200</v>
       </c>
       <c r="D12" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E12" t="n">
         <v>8050</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>8200</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-1.83</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>141</v>
       </c>
       <c r="D13" t="n">
+        <v>137</v>
+      </c>
+      <c r="E13" t="n">
         <v>127</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>141</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-9.93</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>324</v>
       </c>
       <c r="D14" t="n">
+        <v>314</v>
+      </c>
+      <c r="E14" t="n">
         <v>280</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>314</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>-3.09</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-13.58</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>66</v>
       </c>
       <c r="D15" t="n">
+        <v>66</v>
+      </c>
+      <c r="E15" t="n">
         <v>60</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>67</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-9.09</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>117</v>
       </c>
       <c r="D16" t="n">
+        <v>116</v>
+      </c>
+      <c r="E16" t="n">
         <v>107</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>117</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-8.550000000000001</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>101</v>
       </c>
       <c r="D17" t="n">
+        <v>93</v>
+      </c>
+      <c r="E17" t="n">
         <v>101</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>114</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>12.87</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>1030</v>
       </c>
       <c r="D18" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E18" t="n">
         <v>1000</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1065</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>3.4</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-2.91</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>1840</v>
       </c>
       <c r="D19" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E19" t="n">
         <v>1600</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1845</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-13.04</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
